--- a/Delhi_NCR_BESS_Sites_and_Companies.xlsx
+++ b/Delhi_NCR_BESS_Sites_and_Companies.xlsx
@@ -11,8 +11,9 @@
     <sheet name="Installed BESS" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Upcoming BESS" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="NCR Companies" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Visit Plan" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Sources" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Gurgaon-Faridabad" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Visit Plan" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Sources" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="391">
   <si>
     <t xml:space="preserve">BESS Installed in Delhi NCR – Ratings &amp; Contacts</t>
   </si>
@@ -77,6 +78,9 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
+    <t xml:space="preserve">Phone / Mobile (officially published)</t>
+  </si>
+  <si>
     <t xml:space="preserve">BRPL 33/11 kV Kilokari substation (Ashram–Kilokri)</t>
   </si>
   <si>
@@ -110,6 +114,9 @@
     <t xml:space="preserve">India's first DERC-approved commercial standalone BESS; 2 h day + 2 h night supply; ~1 lakh residents; 12-yr life</t>
   </si>
   <si>
+    <t xml:space="preserve">BRPL office 011-49209999 | Helpline 19123 | WhatsApp 8800919123</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tata Power-DDL Rohini substation</t>
   </si>
   <si>
@@ -140,6 +147,9 @@
     <t xml:space="preserve">India's first grid-scale BESS; peak management, frequency regulation, backup to critical loads</t>
   </si>
   <si>
+    <t xml:space="preserve">TPDDL toll-free 19124 / 1800-208-9124</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tata Power-DDL Rani Bagh substation</t>
   </si>
   <si>
@@ -200,6 +210,9 @@
     <t xml:space="preserve">Cumulative 410 kWh; exact sites not public – ask TERI</t>
   </si>
   <si>
+    <t xml:space="preserve">TERI 011-2468 2100 / 011-7110 2100 | mailbox@teri.res.in</t>
+  </si>
+  <si>
     <t xml:space="preserve">BYPL solar + Li-ion microgrids at 4 BYPL offices</t>
   </si>
   <si>
@@ -230,6 +243,9 @@
     <t xml:space="preserve">Behind-the-meter; sizes not published</t>
   </si>
   <si>
+    <t xml:space="preserve">BYPL helpline 19122</t>
+  </si>
+  <si>
     <t xml:space="preserve">BYPL 5 × 200 kWh BESS (tender CMC/BY/20-21/RB/SV/29)</t>
   </si>
   <si>
@@ -305,6 +321,9 @@
     <t xml:space="preserve">Part of 55.5 MW / 111 MWh batch</t>
   </si>
   <si>
+    <t xml:space="preserve">BRPL office 011-49209999 | Helpline 19123 | WhatsApp 8800919123 | TERI 011-2468 2100 / 011-7110 2100 | mailbox@teri.res.in</t>
+  </si>
+  <si>
     <t xml:space="preserve">66/11 kV G5 Matiala</t>
   </si>
   <si>
@@ -392,6 +411,9 @@
     <t xml:space="preserve">4-hour system; no capital subsidy</t>
   </si>
   <si>
+    <t xml:space="preserve">NPCL 0120-622 6666 (via directory – verify)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TPDDL distribution-transformer BESS pilot (ADB grant)</t>
   </si>
   <si>
@@ -458,6 +480,9 @@
     <t xml:space="preserve">High</t>
   </si>
   <si>
+    <t xml:space="preserve">Not published; finance@goodenough.energy; regd. office C-85, Sector 88, Noida 201305</t>
+  </si>
+  <si>
     <t xml:space="preserve">SPML Infra Ltd</t>
   </si>
   <si>
@@ -476,6 +501,9 @@
     <t xml:space="preserve">spml.co.in; investor.relations@spml.co.in</t>
   </si>
   <si>
+    <t xml:space="preserve">Not published; investor.relations@spml.co.in</t>
+  </si>
+  <si>
     <t xml:space="preserve">ACME Solar Holdings</t>
   </si>
   <si>
@@ -497,6 +525,9 @@
     <t xml:space="preserve">Medium</t>
   </si>
   <si>
+    <t xml:space="preserve">Not published – use website contact form</t>
+  </si>
+  <si>
     <t xml:space="preserve">Exicom Tele-Systems</t>
   </si>
   <si>
@@ -683,6 +714,9 @@
     <t xml:space="preserve">UPERC-approved BESS tender</t>
   </si>
   <si>
+    <t xml:space="preserve">0120-622 6666 (via directory – verify)</t>
+  </si>
+  <si>
     <t xml:space="preserve">AmpereHour Energy (outside NCR – Pune)</t>
   </si>
   <si>
@@ -734,6 +768,153 @@
     <t xml:space="preserve">BRPL LoI Oct 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">BESS in Gurgaon &amp; Faridabad (Haryana NCR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As of 30 Oct 2026, no utility-scale BESS is publicly reported as installed inside Gurugram or Faridabad. Both cities are served by DHBVN, whose first BESS tenders are sited elsewhere in Haryana. Rooftop/C&amp;I batteries exist in malls, offices and data centres but sizes aren't published – ask the suppliers below for reference sites.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project / Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner / Buyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phone / contact (official)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHBVN 10 MW/20 MWh standalone BESS (VGF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33 kV Jaglan, Khera, Siwani, Bhiwani + others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHBVN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tender (bids Sep 2025); Haryana targets commissioning by Jul 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dhbvn.org.in; DHBVN helpline 1912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Haryana discom BESS; not in Gurugram/Faridabad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHBVN 4 × 2.5 MW/5 MWh BESS (RfS 7/DHBVNL/BESS/Ph-I)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33 kV substations, DHBVN &amp; UHBVN areas (sites not named)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tendered Aug 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dhbvn.org.in; helpline 1912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask DHBVN if any site is in Gurugram/Faridabad circles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SJVN 265 MW/530 MWh standalone BESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panipat Thermal Power Station (~100 km from Gurgaon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SJVN / Haryana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awarded to NLC India Renewables (Sep 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sjvn.nic.in; nlcindia.in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Largest Haryana BESS; under development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACME Solar Holdings (HQ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~4.96 GWh BESS operating in Rajasthan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acmesolar.in – contact form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best Gurgaon-based utility BESS contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telecom/data-centre Li-ion storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exicom.in – contact form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can show C&amp;I/telecom installs in Gurgaon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCS, containerised BESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power conversion side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home/C&amp;I Li-ion storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large dealer network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C&amp;I BESS integrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask for Gurgaon C&amp;I reference sites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loom Solar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faridabad (Haryana)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar + BESS for homes, offices, hospitals, schools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loomsolar.com – contact form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faridabad-based; does site assessment visits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PURE Energy (PuREPower)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serves Gurugram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential BESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92400 45993 / 92400 38453; WhatsApp 90591 02777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbers from its Gurugram service page</t>
+  </si>
+  <si>
     <t xml:space="preserve">How to arrange visits</t>
   </si>
   <si>
@@ -945,6 +1126,78 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.blackridgeresearch.com/blog/latest-list-of-top-largest-bess-battery-energy-storage-system-companies-manufacturers-india</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRPL contact page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bsesdelhi.com/web/brpl/about-us</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPDDL website (toll-free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tatapower-ddl.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERI contact page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://teriin.org/contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoodEnough registered details (Tofler)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tofler.in/good-enough-energy-private-limited/company/U35105UP2023PTC184184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPCL number (directory – verify)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.indiacustomercare.com/noida-power-company-limited-npcl-contact-no-0120-622-6666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHBVN 10 MW/20 MWh BESS tender (Saur Energy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.saurenergy.com/solar-energy-news/haryana-discom-floats-first-10-mw20-mwh-bess-tender-with-vgf-support-9674182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHBVN 4 x 2.5 MW BESS tender (SolarQuarter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://solarquarter.com/2025/08/19/haryana-issues-tender-for-four-2-5mw-5-mwh-battery-energy-storage-projects-to-strengthen-power-grid/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haryana 20 MWh by Jul 2027 (T&amp;D India)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tndindia.com/haryana-to-commission-20-mwh-vgf-backed-bess-capacity-by-july-2027/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SJVN 265 MW BESS awarded to NIRL (Renewable Watch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://renewablewatch.in/2026/09/28/nirl-wins-sjvns-265-mw-bess-auction/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SJVN BESS at Panipat TPS (Construction World)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.constructionworld.in/policy-updates-and-economic-news/sjvn-invites-bids-for-265-mw-bess-at-panipat-thermal-power-station/95212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PURE Energy Gurugram page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pureenergy.co.in/residential-bess-energy-storage/haryana/gurugram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loom Solar Faridabad (WindySolar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://windysolar.com/bess-company-in-faridabad-haryana/</t>
   </si>
 </sst>
 </file>
@@ -1118,16 +1371,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1143,20 +1400,32 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1301,22 +1570,26 @@
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1407,17 +1680,17 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="40876528"/>
-        <c:axId val="34404784"/>
+        <c:axId val="68907952"/>
+        <c:axId val="55234238"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="40876528"/>
+        <c:axId val="68907952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1443,7 +1716,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34404784"/>
+        <c:crossAx val="55234238"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1451,7 +1724,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="34404784"/>
+        <c:axId val="55234238"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1501,7 +1774,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0##" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0##" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1527,7 +1800,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40876528"/>
+        <c:crossAx val="68907952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1566,9 +1839,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1505520</xdr:colOff>
+      <xdr:colOff>1505160</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>24480</xdr:rowOff>
+      <xdr:rowOff>24120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1576,8 +1849,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="281880" y="3638520"/>
-        <a:ext cx="7919640" cy="3239640"/>
+        <a:off x="281880" y="3591720"/>
+        <a:ext cx="7919280" cy="3223800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1770,384 +2043,406 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="P4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="C5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <f aca="false">IF(AND(ISNUMBER(D5),ISNUMBER(E5),D5&gt;0),E5/D5,"-")</f>
         <v>2</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="J5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="L5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="M5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="N5" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="O5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="5" t="n">
+      <c r="B6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <f aca="false">IF(AND(ISNUMBER(D6),ISNUMBER(E6),D6&gt;0),E6/D6,"-")</f>
         <v>1</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>0.528</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <f aca="false">IF(AND(ISNUMBER(D7),ISNUMBER(E7),D7&gt;0),E7/D7,"-")</f>
         <v>3.52</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="P7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5" t="n">
+      <c r="B8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6" t="n">
         <v>0.41</v>
       </c>
-      <c r="F8" s="5" t="str">
+      <c r="F8" s="6" t="str">
         <f aca="false">IF(AND(ISNUMBER(D8),ISNUMBER(E8),D8&gt;0),E8/D8,"-")</f>
         <v>-</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="J8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="K8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="L8" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="M8" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5" t="str">
+      <c r="B9" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="str">
         <f aca="false">IF(AND(ISNUMBER(D9),ISNUMBER(E9),D9&gt;0),E9/D9,"-")</f>
         <v>-</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="L9" s="4" t="s">
+      <c r="G9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="J9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="L9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5" t="n">
+      <c r="B10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="5" t="str">
+      <c r="F10" s="6" t="str">
         <f aca="false">IF(AND(ISNUMBER(D10),ISNUMBER(E10),D10&gt;0),E10/D10,"-")</f>
         <v>-</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="L10" s="4" t="s">
+      <c r="G10" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="P10" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="6" t="n">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C11" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="7" t="n">
         <f aca="false">SUM(D5:D10)</f>
         <v>30.15</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <f aca="false">SUM(E5:E10)</f>
         <v>51.938</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
-        <v>78</v>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="8" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2166,416 +2461,453 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" s="6" t="n">
         <v>80</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="F13" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C16" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>320</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="9" t="n">
         <f aca="false">SUM(D5:D15)</f>
         <v>233</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="9" t="n">
         <f aca="false">SUM(E5:E15)</f>
         <v>626</v>
       </c>
@@ -2597,495 +2929,550 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>129</v>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="B4" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="B5" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="B6" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="I15" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="I18" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
+      <c r="B20" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>156</v>
+      <c r="B21" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -3104,124 +3491,390 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>237</v>
-      </c>
+      <c r="A1" s="11" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>242</v>
+      <c r="B5" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="B6" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="B7" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>530</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="B8" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="B9" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="B10" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="B11" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>256</v>
+      <c r="B12" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3237,213 +3890,442 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="120"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="110"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>258</v>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="A4" s="4" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>306</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>316</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B39"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="120"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>
